--- a/src/cubes/data/energy_systems/hvac-schema.xlsx
+++ b/src/cubes/data/energy_systems/hvac-schema.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/housing_stock/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/energy_systems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649B2A4F-3EC4-1B43-B18A-6EA7D244B110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F808196-7807-AB46-97F5-67BE200E7F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25040" windowHeight="13440" xr2:uid="{4DAF8F1F-FDB7-8C42-B032-28677CD2A744}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$21</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
   <si>
     <t>Central fueloil condensing boiler</t>
   </si>
@@ -62,9 +56,6 @@
     <t>ZoneHVAC:HighTemperatureRadiant</t>
   </si>
   <si>
-    <t>How do we model individual heating systems in a building shell?</t>
-  </si>
-  <si>
     <t>Individual gas low temperature non-condensing boiler </t>
   </si>
   <si>
@@ -77,9 +68,6 @@
     <t>DistrictHeating</t>
   </si>
   <si>
-    <t>Do we need to specify Hotwater inlet and outlet nodes? </t>
-  </si>
-  <si>
     <t>Central gas non-condensing boiler new</t>
   </si>
   <si>
@@ -89,9 +77,6 @@
     <t>ZoneHVAC:LowTemperatureRadiant:Electric</t>
   </si>
   <si>
-    <t>May need to specify surface name</t>
-  </si>
-  <si>
     <t>Central gas condensing boiler</t>
   </si>
   <si>
@@ -113,9 +98,6 @@
     <t>Individual wood stove</t>
   </si>
   <si>
-    <t>Fuel type cannot be wood so </t>
-  </si>
-  <si>
     <t>Individual electric convector heater</t>
   </si>
   <si>
@@ -141,6 +123,9 @@
   </si>
   <si>
     <t>HEATING SYSTEM 1 TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>HEATING SYSTEM TYPE</t>
   </si>
 </sst>
 </file>
@@ -514,227 +499,211 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2DC506-9992-2C48-B098-2854D27BB987}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21" xr:uid="{3E2DC506-9992-2C48-B098-2854D27BB987}"/>
+  <autoFilter ref="A1:C21" xr:uid="{3E2DC506-9992-2C48-B098-2854D27BB987}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>